--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/TENNESSEE_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/TENNESSEE_2012.xlsx
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C155">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C180">
@@ -6799,7 +6799,7 @@
         <v>82</v>
       </c>
       <c r="D358">
-        <v>0.009430707303048</v>
+        <v>0.009430707303048002</v>
       </c>
     </row>
     <row r="359">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C608">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C690">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C718">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1110">
